--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487969_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487969_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>F. SERRANO RUBIO</t>
+          <t>Z. POPE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0909</v>
+        <v>2.2287</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7076</v>
+        <v>0.9092</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3833</v>
+        <v>1.3194</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6026</v>
+        <v>1.1761</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.438</v>
+        <v>1.6678</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1646</v>
+        <v>-0.4917</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.8300999999999999</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.9144</v>
+        <v>1.594</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0842</v>
+        <v>-0.639</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7725</v>
+        <v>0.221</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.0738</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.2488</v>
+        <v>0.1472</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1.1893</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0216</v>
+        <v>-0.1368</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0552</v>
+        <v>-0.0459</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0335</v>
+        <v>-0.09089999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6808</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Z. POPE</t>
+          <t>F. SERRANO RUBIO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8783</v>
+        <v>2.2271</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6431</v>
+        <v>1.8719</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2352</v>
+        <v>0.3552</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1761</v>
+        <v>-1.6026</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6678</v>
+        <v>-1.438</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4917</v>
+        <v>-0.1646</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9550999999999999</v>
+        <v>-0.8300999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>1.594</v>
+        <v>-0.9144</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.639</v>
+        <v>0.0842</v>
       </c>
       <c r="M3" t="n">
-        <v>0.221</v>
+        <v>-0.7725</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0738</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1472</v>
+        <v>-0.2488</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R3" t="n">
         <v>1.1893</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4871</v>
+        <v>0.1578</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.312</v>
+        <v>0.2194</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1752</v>
+        <v>-0.0616</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.6808</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. PEREIRA FERNANDES</t>
+          <t>A. MIR AMATE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2667</v>
+        <v>1.8813</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1521</v>
+        <v>-0.4515</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4188</v>
+        <v>2.3328</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9658</v>
+        <v>1.4734</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0723</v>
+        <v>1.3031</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8935</v>
+        <v>0.1703</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0745</v>
+        <v>0.9768</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4641</v>
+        <v>1.0896</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6104000000000001</v>
+        <v>-0.1128</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1087</v>
+        <v>0.4966</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3918</v>
+        <v>0.2136</v>
       </c>
       <c r="O4" t="n">
         <v>0.2831</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0163</v>
+        <v>0.7268</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5616</v>
+        <v>0.2873</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5453</v>
+        <v>0.4395</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.674</v>
+        <v>-0.1207</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.674</v>
+        <v>0.2666</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3873</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MIR AMATE</t>
+          <t>R. PEREIRA FERNANDES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.24</v>
+        <v>1.6491</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2894</v>
+        <v>-0.3766</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5293</v>
+        <v>2.0257</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4734</v>
+        <v>0.9658</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3031</v>
+        <v>0.0723</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1703</v>
+        <v>0.8935</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9768</v>
+        <v>1.0745</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0896</v>
+        <v>0.4641</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1128</v>
+        <v>0.6104000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4966</v>
+        <v>-0.1087</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2136</v>
+        <v>-0.3918</v>
       </c>
       <c r="O5" t="n">
         <v>0.2831</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.3661</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5505</v>
+        <v>0.2139</v>
       </c>
       <c r="U5" t="n">
-        <v>0.636</v>
+        <v>0.1522</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1207</v>
+        <v>-0.674</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GARCÍA GAZQUEZ</t>
+          <t>M. VIGO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.208</v>
+        <v>1.214</v>
       </c>
       <c r="E6" t="n">
-        <v>1.208</v>
+        <v>3.1168</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-1.9028</v>
       </c>
       <c r="G6" t="n">
-        <v>1.208</v>
+        <v>0.983</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6052999999999999</v>
+        <v>3.692</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6027</v>
+        <v>-2.709</v>
       </c>
       <c r="J6" t="n">
-        <v>1.208</v>
+        <v>1.2781</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6052999999999999</v>
+        <v>3.8741</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6027</v>
+        <v>-2.596</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.2952</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.1822</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.113</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.8298</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.046</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.5349</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.742</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. VIGO RODRIGUEZ</t>
+          <t>D. GARCÍA GAZQUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9913</v>
+        <v>1.208</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3995</v>
+        <v>1.208</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.4082</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.983</v>
+        <v>1.208</v>
       </c>
       <c r="H7" t="n">
-        <v>3.692</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.709</v>
+        <v>0.6027</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2781</v>
+        <v>1.208</v>
       </c>
       <c r="K7" t="n">
-        <v>3.8741</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.596</v>
+        <v>0.6027</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2952</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1822</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.113</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5610000000000001</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1125</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5514</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.5349</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.742</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>G. LOPEZ TORRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2435</v>
+        <v>-0.2934</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7917</v>
+        <v>0.4673</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0352</v>
+        <v>-0.7607</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5075</v>
+        <v>0.4659</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5114</v>
+        <v>1.1393</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0039</v>
+        <v>-0.6734</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2123</v>
+        <v>0.5921</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5655</v>
+        <v>1.2712</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6467000000000001</v>
+        <v>-0.6791</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7048</v>
+        <v>-0.1262</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0542</v>
+        <v>-0.1319</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6506</v>
+        <v>0.0057</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7751</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1627</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1742</v>
+        <v>-0.3451</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2886</v>
+        <v>-0.1248</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8856000000000001</v>
+        <v>-0.2203</v>
       </c>
       <c r="V8" t="n">
-        <v>0.337</v>
+        <v>-1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5331</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. LOPEZ TORRE</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4057</v>
+        <v>-0.7056</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4673</v>
+        <v>-1.5442</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.873</v>
+        <v>0.8387</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4659</v>
+        <v>0.5075</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1393</v>
+        <v>0.5114</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6734</v>
+        <v>-0.0039</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5921</v>
+        <v>1.2123</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2712</v>
+        <v>0.5655</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6791</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1262</v>
+        <v>-0.7048</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1319</v>
+        <v>-0.0542</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0057</v>
+        <v>-0.6506</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7929</v>
+        <v>-2.7751</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.1627</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4574</v>
+        <v>1.2251</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1248</v>
+        <v>0.5361</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3326</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2071</v>
+        <v>0.337</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2071</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. WRIGHT RODRIGUEZ</t>
+          <t>A. PEREZ GARCIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8468</v>
+        <v>-1.1753</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0386</v>
+        <v>-3.0153</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1918</v>
+        <v>1.8401</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8519</v>
+        <v>-3.1668</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1752</v>
+        <v>-1.3627</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3232</v>
+        <v>-1.8041</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4184</v>
+        <v>-3.1337</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4586</v>
+        <v>-1.1767</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>-1.957</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5665</v>
+        <v>-0.0331</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2834</v>
+        <v>-0.1861</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2831</v>
+        <v>0.1529</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.784</v>
+        <v>0.5947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9733</v>
+        <v>-1.1893</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>2.443</v>
+        <v>-0.3634</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3532</v>
+        <v>-0.166</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0898</v>
+        <v>-0.1974</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6539</v>
+        <v>1.7604</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6539</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.376</v>
+        <v>-1.3479</v>
       </c>
       <c r="E11" t="n">
         <v>-0.9911</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3848</v>
+        <v>-0.3568</v>
       </c>
       <c r="G11" t="n">
         <v>-0.4036</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5999</v>
+        <v>-1.5719</v>
       </c>
       <c r="E12" t="n">
         <v>-1.0133</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5866</v>
+        <v>-0.5585</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2935</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3153</v>
+        <v>-0.2873</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0624</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2529</v>
+        <v>-0.2249</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. PEREZ GARCIA</t>
+          <t>D. WRIGHT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7813</v>
+        <v>-2.1867</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6495</v>
+        <v>-3.2381</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8682</v>
+        <v>1.0514</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.1668</v>
+        <v>-0.8519</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.3627</v>
+        <v>-1.1752</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8041</v>
+        <v>0.3232</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.1337</v>
+        <v>-1.4184</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.1767</v>
+        <v>-1.4586</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.957</v>
+        <v>0.0402</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0331</v>
+        <v>0.5665</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1861</v>
+        <v>0.2834</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1529</v>
+        <v>0.2831</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5947</v>
+        <v>-1.784</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1893</v>
+        <v>-2.9733</v>
       </c>
       <c r="R13" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9695</v>
+        <v>1.1031</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8001</v>
+        <v>1.1537</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1694</v>
+        <v>-0.0506</v>
       </c>
       <c r="V13" t="n">
-        <v>1.7604</v>
+        <v>-0.6539</v>
       </c>
       <c r="W13" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2867</v>
+        <v>-0.6539</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.2021</v>
+        <v>-2.4847</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.2405</v>
+        <v>-4.7477</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0384</v>
+        <v>2.263</v>
       </c>
       <c r="G14" t="n">
         <v>0.2465</v>
@@ -1546,13 +1546,13 @@
         <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1718</v>
+        <v>0.8892</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2461</v>
+        <v>0.7389</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0743</v>
+        <v>0.1503</v>
       </c>
       <c r="V14" t="n">
         <v>0.1459</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2930999999999995</v>
+        <v>0.6426999999999996</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.7407</v>
+        <v>-7.804600000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>8.447600000000001</v>
+        <v>8.447499999999998</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7078</v>
+        <v>0.7077999999999998</v>
       </c>
       <c r="H15" t="n">
         <v>3.3956</v>
@@ -1597,7 +1597,7 @@
         <v>-2.6879</v>
       </c>
       <c r="J15" t="n">
-        <v>2.416999999999998</v>
+        <v>2.416999999999999</v>
       </c>
       <c r="K15" t="n">
         <v>5.2759</v>
@@ -1615,7 +1615,7 @@
         <v>0.1712000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.9644</v>
+        <v>-3.964399999999999</v>
       </c>
       <c r="Q15" t="n">
         <v>-19.8221</v>
@@ -1624,16 +1624,16 @@
         <v>15.8578</v>
       </c>
       <c r="S15" t="n">
-        <v>3.230200000000001</v>
+        <v>4.1661</v>
       </c>
       <c r="T15" t="n">
-        <v>2.644200000000001</v>
+        <v>3.58</v>
       </c>
       <c r="U15" t="n">
         <v>0.5861</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2665000000000005</v>
+        <v>-0.2665000000000004</v>
       </c>
       <c r="W15" t="n">
         <v>6.0205</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1396</v>
+        <v>5.8189</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6395</v>
+        <v>2.4357</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5001</v>
+        <v>3.3832</v>
       </c>
       <c r="G16" t="n">
         <v>4.1074</v>
@@ -1702,13 +1702,13 @@
         <v>3.3698</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1949</v>
+        <v>-0.1257</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2461</v>
+        <v>0.0424</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0513</v>
+        <v>-0.1681</v>
       </c>
       <c r="V16" t="n">
         <v>3.6213</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MUNOZ LEIVA</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.8745</v>
+        <v>4.2633</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9714</v>
+        <v>0.9601</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0969</v>
+        <v>3.3032</v>
       </c>
       <c r="G17" t="n">
-        <v>2.0788</v>
+        <v>0.1512</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3175</v>
+        <v>-1.473</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7613</v>
+        <v>1.6242</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9102</v>
+        <v>0.5163</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7093</v>
+        <v>-0.8135</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2009</v>
+        <v>1.3298</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1686</v>
+        <v>-0.365</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3918</v>
+        <v>-0.6595</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5604</v>
+        <v>0.2945</v>
       </c>
       <c r="P17" t="n">
-        <v>2.1805</v>
+        <v>0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3787</v>
+        <v>2.7751</v>
       </c>
       <c r="S17" t="n">
-        <v>2.1593</v>
+        <v>-0.1744</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4597</v>
+        <v>-0.3935</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3004</v>
+        <v>0.2192</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5441</v>
+        <v>3.6917</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7997</v>
+        <v>3.0178</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3438</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>J. MUNOZ LEIVA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1826</v>
+        <v>3.3347</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0433</v>
+        <v>3.2396</v>
       </c>
       <c r="F18" t="n">
-        <v>3.1393</v>
+        <v>0.0951</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1512</v>
+        <v>2.0788</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.473</v>
+        <v>1.3175</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6242</v>
+        <v>0.7613</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5163</v>
+        <v>1.9102</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8135</v>
+        <v>1.7093</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3298</v>
+        <v>0.2009</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.365</v>
+        <v>0.1686</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6595</v>
+        <v>-0.3918</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2945</v>
+        <v>0.5604</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5947</v>
+        <v>2.1805</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7751</v>
+        <v>2.3787</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2551</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3103</v>
+        <v>0.7279</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0553</v>
+        <v>-0.1084</v>
       </c>
       <c r="V18" t="n">
-        <v>3.6917</v>
+        <v>-1.5441</v>
       </c>
       <c r="W18" t="n">
-        <v>3.0178</v>
+        <v>0.7997</v>
       </c>
       <c r="X18" t="n">
-        <v>0.674</v>
+        <v>-2.3438</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MUÑOZ LEIVA</t>
+          <t>P. CARRASCO LOBO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6027</v>
+        <v>0.6096</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6027</v>
+        <v>1.6381</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-1.0284</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6027</v>
+        <v>1.2272</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-0.5463</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6027</v>
+        <v>1.7735</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6027</v>
+        <v>2.0133</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.1211</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6027</v>
+        <v>1.8922</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.7861</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.6674</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.1187</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.1945</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.177</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.0175</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. RAGA RODRÍGUEZ</t>
+          <t>J. MUÑOZ LEIVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,31 +1969,31 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3027</v>
+        <v>0.6027</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6027</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CARRASCO LOBO</t>
+          <t>R. RAGA RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2321</v>
+        <v>0.3027</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1287</v>
+        <v>0.3027</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3608</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.2272</v>
+        <v>0.3027</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.5463</v>
+        <v>0.3027</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7735</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0133</v>
+        <v>0.3027</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1211</v>
+        <v>0.3027</v>
       </c>
       <c r="L21" t="n">
-        <v>1.8922</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7861</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6674</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1187</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0362</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6864</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3499</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7012</v>
+        <v>-0.8506</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2882</v>
+        <v>-0.6919</v>
       </c>
       <c r="F23" t="n">
-        <v>2.587</v>
+        <v>-0.1587</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5433</v>
+        <v>-0.4404</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2027</v>
+        <v>-1.2899</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.746</v>
+        <v>0.8494</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.3098</v>
+        <v>-0.4016</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1211</v>
+        <v>-0.968</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4308</v>
+        <v>0.5664</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7665</v>
+        <v>-0.0388</v>
       </c>
       <c r="N23" t="n">
-        <v>0.08160000000000001</v>
+        <v>-0.3219</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6848</v>
+        <v>0.2831</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R23" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0403</v>
+        <v>-0.2735</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0038</v>
+        <v>0.4342</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0365</v>
+        <v>-0.7077</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4651</v>
+        <v>-0.982</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9976</v>
+        <v>-3.2882</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4675</v>
+        <v>2.3062</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4404</v>
+        <v>-0.5433</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2899</v>
+        <v>0.2027</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8494</v>
+        <v>-0.746</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4016</v>
+        <v>-1.3098</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.968</v>
+        <v>0.1211</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5664</v>
+        <v>-1.4308</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0388</v>
+        <v>0.7665</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.3219</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2831</v>
+        <v>0.6848</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3964</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8879</v>
+        <v>-0.2405</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1286</v>
+        <v>0.0038</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0165</v>
+        <v>-0.2442</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5331</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9915</v>
+        <v>-2.733</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.3441</v>
+        <v>-2.7766</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3526</v>
+        <v>0.0436</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3598</v>
+        <v>-1.0928</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.0532</v>
+        <v>-0.6068</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3067</v>
+        <v>-0.486</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7078</v>
+        <v>-0.2487</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3897</v>
+        <v>0.3903</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3181</v>
+        <v>-0.639</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.652</v>
+        <v>-0.8442</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6634</v>
+        <v>-0.9971</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0114</v>
+        <v>0.1529</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7929</v>
+        <v>0.7929</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R25" t="n">
-        <v>1.1893</v>
+        <v>1.784</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4982</v>
+        <v>-0.8186</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6829</v>
+        <v>-0.1889</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1847</v>
+        <v>-0.6297</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.337</v>
+        <v>-1.6145</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.337</v>
+        <v>-1.3479</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.2881</v>
+        <v>-3.7889</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.3878</v>
+        <v>-4.0572</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0998</v>
+        <v>0.2683</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.0928</v>
+        <v>-2.3598</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6068</v>
+        <v>-1.0532</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.486</v>
+        <v>-1.3067</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2487</v>
+        <v>-1.7078</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3903</v>
+        <v>-0.3897</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.639</v>
+        <v>-1.3181</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.8442</v>
+        <v>-0.652</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.9971</v>
+        <v>-0.6634</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1529</v>
+        <v>0.0114</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7929</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R26" t="n">
-        <v>1.784</v>
+        <v>1.1893</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3736</v>
+        <v>-0.2991</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8001</v>
+        <v>-0.0302</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5735</v>
+        <v>-0.269</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.6145</v>
+        <v>-0.337</v>
       </c>
       <c r="W26" t="n">
-        <v>-1.3479</v>
+        <v>-0.337</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.7616</v>
+        <v>-5.236</v>
       </c>
       <c r="E27" t="n">
-        <v>-6.5631</v>
+        <v>-6.2575</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8015</v>
+        <v>1.0215</v>
       </c>
       <c r="G27" t="n">
         <v>-4.7576</v>
@@ -2560,13 +2560,13 @@
         <v>2.5769</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.1845</v>
+        <v>-0.6589</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.0608</v>
+        <v>-0.7551</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1238</v>
+        <v>0.0963</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2071</v>
@@ -2593,19 +2593,19 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2933999999999983</v>
+        <v>0.9723000000000015</v>
       </c>
       <c r="E28" t="n">
         <v>-8.4473</v>
       </c>
       <c r="F28" t="n">
-        <v>8.7409</v>
+        <v>9.419799999999999</v>
       </c>
       <c r="G28" t="n">
         <v>-0.7074999999999996</v>
       </c>
       <c r="H28" t="n">
-        <v>-3.3957</v>
+        <v>-3.395700000000001</v>
       </c>
       <c r="I28" t="n">
         <v>2.688000000000001</v>
@@ -2617,13 +2617,13 @@
         <v>1.8805</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.1710000000000007</v>
+        <v>-0.1709999999999998</v>
       </c>
       <c r="M28" t="n">
         <v>-2.417</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.276199999999999</v>
+        <v>-5.2762</v>
       </c>
       <c r="O28" t="n">
         <v>2.8591</v>
@@ -2638,16 +2638,16 @@
         <v>19.8223</v>
       </c>
       <c r="S28" t="n">
-        <v>-3.23</v>
+        <v>-2.5511</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.5860999999999996</v>
+        <v>-0.5860000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.6441</v>
+        <v>-1.9649</v>
       </c>
       <c r="V28" t="n">
-        <v>0.2665000000000002</v>
+        <v>0.2665000000000004</v>
       </c>
       <c r="W28" t="n">
         <v>6.2871</v>
